--- a/results/master_pareto.xlsx
+++ b/results/master_pareto.xlsx
@@ -1,28 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Documents\GitHub\logistics-model2\internal-logistics-model2\results\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="12" windowWidth="16092" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Q$16</definedName>
-  </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="54">
   <si>
     <t>run_id</t>
   </si>
@@ -120,6 +112,12 @@
     <t>SR_SV_WT_case3_P5_eps85</t>
   </si>
   <si>
+    <t>SR_SV_RD_case2_P10_eps9999</t>
+  </si>
+  <si>
+    <t>SR_SV_RD_case3_P10_eps9999</t>
+  </si>
+  <si>
     <t>SR_SV_RD</t>
   </si>
   <si>
@@ -169,16 +167,22 @@
   </si>
   <si>
     <t>2026_05_06_19_29</t>
+  </si>
+  <si>
+    <t>2026_05_13_21_45</t>
+  </si>
+  <si>
+    <t>2026_05_13_21_46</t>
+  </si>
+  <si>
+    <t>2026_05_13_21_49</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000"/>
-  </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,31 +234,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Teması">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -296,7 +291,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -328,10 +323,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -363,7 +357,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -539,31 +532,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:Q16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.21875" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -616,15 +589,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -639,16 +612,16 @@
         <v>91</v>
       </c>
       <c r="H2">
-        <v>77.090999999999994</v>
-      </c>
-      <c r="I2" s="2">
-        <v>77.090999999999994</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="2">
-        <v>2.5490000247955318</v>
+        <v>77.09099999999999</v>
+      </c>
+      <c r="I2">
+        <v>77.09099999999999</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>2.549000024795532</v>
       </c>
       <c r="L2">
         <v>2</v>
@@ -657,18 +630,18 @@
         <v>5</v>
       </c>
       <c r="N2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -685,14 +658,14 @@
       <c r="H3">
         <v>79.09</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3">
         <v>79.09</v>
       </c>
-      <c r="J3" s="2">
-        <v>0</v>
-      </c>
-      <c r="K3" s="2">
-        <v>1.7330000400543211</v>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>1.733000040054321</v>
       </c>
       <c r="L3">
         <v>2</v>
@@ -701,18 +674,18 @@
         <v>5</v>
       </c>
       <c r="N3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -727,16 +700,16 @@
         <v>89</v>
       </c>
       <c r="H4">
-        <v>81.088999999999999</v>
-      </c>
-      <c r="I4" s="2">
-        <v>81.088999999999999</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0</v>
-      </c>
-      <c r="K4" s="2">
-        <v>2.9819998741149898</v>
+        <v>81.089</v>
+      </c>
+      <c r="I4">
+        <v>81.089</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>2.98199987411499</v>
       </c>
       <c r="L4">
         <v>2</v>
@@ -745,18 +718,18 @@
         <v>5</v>
       </c>
       <c r="N4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" t="s">
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -771,16 +744,16 @@
         <v>85</v>
       </c>
       <c r="H5">
-        <v>67.085000000000008</v>
-      </c>
-      <c r="I5" s="2">
-        <v>67.084999999987815</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0</v>
-      </c>
-      <c r="K5" s="2">
-        <v>0.25499987602233892</v>
+        <v>67.08500000000001</v>
+      </c>
+      <c r="I5">
+        <v>67.08499999998782</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0.2549998760223389</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -789,18 +762,18 @@
         <v>5</v>
       </c>
       <c r="N5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" t="s">
         <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -815,16 +788,16 @@
         <v>85</v>
       </c>
       <c r="H6">
-        <v>67.085000000000008</v>
-      </c>
-      <c r="I6" s="2">
-        <v>66.672577464788745</v>
-      </c>
-      <c r="J6" s="2">
-        <v>6.1477608289671774E-3</v>
-      </c>
-      <c r="K6" s="2">
-        <v>9.4000101089477539E-2</v>
+        <v>67.08500000000001</v>
+      </c>
+      <c r="I6">
+        <v>66.67257746478874</v>
+      </c>
+      <c r="J6">
+        <v>0.006147760828967177</v>
+      </c>
+      <c r="K6">
+        <v>0.09400010108947754</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -833,18 +806,18 @@
         <v>5</v>
       </c>
       <c r="N6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" t="s">
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -861,14 +834,14 @@
       <c r="H7">
         <v>85.13</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7">
         <v>85.13</v>
       </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0.13700008392333979</v>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0.1370000839233398</v>
       </c>
       <c r="L7">
         <v>2</v>
@@ -877,18 +850,18 @@
         <v>5</v>
       </c>
       <c r="N7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" t="s">
         <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -905,14 +878,14 @@
       <c r="H8">
         <v>85.13</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8">
         <v>85.13</v>
       </c>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2">
-        <v>3.9000034332275391E-2</v>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0.03900003433227539</v>
       </c>
       <c r="L8">
         <v>2</v>
@@ -921,18 +894,18 @@
         <v>5</v>
       </c>
       <c r="N8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" t="s">
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D9">
         <v>5</v>
@@ -944,15 +917,15 @@
         <v>89</v>
       </c>
       <c r="H9">
-        <v>89.081000000000003</v>
-      </c>
-      <c r="I9" s="2">
-        <v>89.081000000000003</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2">
+        <v>89.081</v>
+      </c>
+      <c r="I9">
+        <v>89.081</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
         <v>1.559999942779541</v>
       </c>
       <c r="L9">
@@ -962,21 +935,21 @@
         <v>5</v>
       </c>
       <c r="N9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O9">
         <v>9999</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17">
       <c r="A10" t="s">
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -988,15 +961,15 @@
         <v>90</v>
       </c>
       <c r="H10">
-        <v>90.079000000000008</v>
-      </c>
-      <c r="I10" s="2">
+        <v>90.07900000000001</v>
+      </c>
+      <c r="I10">
         <v>90.07899999999961</v>
       </c>
-      <c r="J10" s="2">
-        <v>0</v>
-      </c>
-      <c r="K10" s="2">
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
         <v>2.872999906539917</v>
       </c>
       <c r="L10">
@@ -1006,21 +979,21 @@
         <v>5</v>
       </c>
       <c r="N10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O10">
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17">
       <c r="A11" t="s">
         <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D11">
         <v>5</v>
@@ -1032,16 +1005,16 @@
         <v>91</v>
       </c>
       <c r="H11">
-        <v>91.076999999999998</v>
-      </c>
-      <c r="I11" s="2">
-        <v>91.076999999999998</v>
-      </c>
-      <c r="J11" s="2">
-        <v>0</v>
-      </c>
-      <c r="K11" s="2">
-        <v>2.8550000190734859</v>
+        <v>91.077</v>
+      </c>
+      <c r="I11">
+        <v>91.077</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>2.855000019073486</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -1050,21 +1023,21 @@
         <v>5</v>
       </c>
       <c r="N11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O11">
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17">
       <c r="A12" t="s">
         <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D12">
         <v>5</v>
@@ -1076,16 +1049,16 @@
         <v>91</v>
       </c>
       <c r="H12">
-        <v>91.076999999999998</v>
-      </c>
-      <c r="I12" s="2">
-        <v>91.076999999999998</v>
-      </c>
-      <c r="J12" s="2">
-        <v>0</v>
-      </c>
-      <c r="K12" s="2">
-        <v>1.7220001220703121</v>
+        <v>91.077</v>
+      </c>
+      <c r="I12">
+        <v>91.077</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>1.722000122070312</v>
       </c>
       <c r="L12">
         <v>2</v>
@@ -1094,21 +1067,21 @@
         <v>5</v>
       </c>
       <c r="N12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O12">
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17">
       <c r="A13" t="s">
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D13">
         <v>5</v>
@@ -1120,15 +1093,15 @@
         <v>85</v>
       </c>
       <c r="H13">
-        <v>85.067000000000007</v>
-      </c>
-      <c r="I13" s="2">
-        <v>85.067000000000007</v>
-      </c>
-      <c r="J13" s="2">
-        <v>0</v>
-      </c>
-      <c r="K13" s="2">
+        <v>85.06700000000001</v>
+      </c>
+      <c r="I13">
+        <v>85.06700000000001</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
         <v>0.1590001583099365</v>
       </c>
       <c r="L13">
@@ -1138,21 +1111,21 @@
         <v>5</v>
       </c>
       <c r="N13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O13">
         <v>9999</v>
       </c>
     </row>
-    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17">
       <c r="A14" t="s">
         <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D14">
         <v>5</v>
@@ -1164,16 +1137,16 @@
         <v>85</v>
       </c>
       <c r="H14">
-        <v>85.067000000000007</v>
-      </c>
-      <c r="I14" s="2">
-        <v>85.067000000000007</v>
-      </c>
-      <c r="J14" s="2">
-        <v>0</v>
-      </c>
-      <c r="K14" s="2">
-        <v>0.16999983787536621</v>
+        <v>85.06700000000001</v>
+      </c>
+      <c r="I14">
+        <v>85.06700000000001</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0.1699998378753662</v>
       </c>
       <c r="L14">
         <v>2</v>
@@ -1182,21 +1155,21 @@
         <v>5</v>
       </c>
       <c r="N14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O14">
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17">
       <c r="A15" t="s">
         <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D15">
         <v>5</v>
@@ -1208,16 +1181,16 @@
         <v>130</v>
       </c>
       <c r="H15">
-        <v>130.08500000000001</v>
-      </c>
-      <c r="I15" s="2">
-        <v>129.32403319775639</v>
-      </c>
-      <c r="J15" s="2">
-        <v>5.8497659395288877E-3</v>
-      </c>
-      <c r="K15" s="2">
-        <v>0.12699985504150391</v>
+        <v>130.085</v>
+      </c>
+      <c r="I15">
+        <v>129.3240331977564</v>
+      </c>
+      <c r="J15">
+        <v>0.005849765939528888</v>
+      </c>
+      <c r="K15">
+        <v>0.1269998550415039</v>
       </c>
       <c r="L15">
         <v>2</v>
@@ -1226,21 +1199,21 @@
         <v>5</v>
       </c>
       <c r="N15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O15">
         <v>9999</v>
       </c>
     </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17">
       <c r="A16" t="s">
         <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D16">
         <v>5</v>
@@ -1252,15 +1225,15 @@
         <v>130</v>
       </c>
       <c r="H16">
-        <v>130.08500000000001</v>
-      </c>
-      <c r="I16" s="2">
+        <v>130.085</v>
+      </c>
+      <c r="I16">
         <v>130.0709999999996</v>
       </c>
-      <c r="J16" s="2">
-        <v>1.076219395044496E-4</v>
-      </c>
-      <c r="K16" s="2">
+      <c r="J16">
+        <v>0.0001076219395044496</v>
+      </c>
+      <c r="K16">
         <v>0.1089999675750732</v>
       </c>
       <c r="L16">
@@ -1270,20 +1243,233 @@
         <v>5</v>
       </c>
       <c r="N16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O16">
         <v>85</v>
       </c>
     </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17">
+        <v>10</v>
+      </c>
+      <c r="E17">
+        <v>9999</v>
+      </c>
+      <c r="F17">
+        <v>102</v>
+      </c>
+      <c r="G17">
+        <v>375</v>
+      </c>
+      <c r="H17">
+        <v>102.375</v>
+      </c>
+      <c r="I17">
+        <v>102.375</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0.7079999446868896</v>
+      </c>
+      <c r="L17">
+        <v>2</v>
+      </c>
+      <c r="M17">
+        <v>10</v>
+      </c>
+      <c r="N17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18">
+        <v>10</v>
+      </c>
+      <c r="E18">
+        <v>9999</v>
+      </c>
+      <c r="F18">
+        <v>102</v>
+      </c>
+      <c r="G18">
+        <v>404</v>
+      </c>
+      <c r="H18">
+        <v>102.404</v>
+      </c>
+      <c r="I18">
+        <v>101.407</v>
+      </c>
+      <c r="J18">
+        <v>0.009735947814538492</v>
+      </c>
+      <c r="K18">
+        <v>0.05500006675720215</v>
+      </c>
+      <c r="L18">
+        <v>2</v>
+      </c>
+      <c r="M18">
+        <v>10</v>
+      </c>
+      <c r="N18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+      <c r="E19">
+        <v>9999</v>
+      </c>
+      <c r="F19">
+        <v>85</v>
+      </c>
+      <c r="G19">
+        <v>130</v>
+      </c>
+      <c r="H19">
+        <v>85.13000000000001</v>
+      </c>
+      <c r="I19">
+        <v>85.12999999999683</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0.1110000610351562</v>
+      </c>
+      <c r="L19">
+        <v>2</v>
+      </c>
+      <c r="M19">
+        <v>5</v>
+      </c>
+      <c r="N19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20">
+        <v>5</v>
+      </c>
+      <c r="E20">
+        <v>9999</v>
+      </c>
+      <c r="F20">
+        <v>67</v>
+      </c>
+      <c r="G20">
+        <v>85</v>
+      </c>
+      <c r="H20">
+        <v>67.08499999999999</v>
+      </c>
+      <c r="I20">
+        <v>67.08499999999522</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0.1570000648498535</v>
+      </c>
+      <c r="L20">
+        <v>2</v>
+      </c>
+      <c r="M20">
+        <v>5</v>
+      </c>
+      <c r="N20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21">
+        <v>5</v>
+      </c>
+      <c r="E21">
+        <v>9999</v>
+      </c>
+      <c r="F21">
+        <v>77</v>
+      </c>
+      <c r="G21">
+        <v>92</v>
+      </c>
+      <c r="H21">
+        <v>77.092</v>
+      </c>
+      <c r="I21">
+        <v>77.09199999999262</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>2.442000150680542</v>
+      </c>
+      <c r="L21">
+        <v>2</v>
+      </c>
+      <c r="M21">
+        <v>5</v>
+      </c>
+      <c r="N21" t="s">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q16">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="case1"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/results/master_pareto.xlsx
+++ b/results/master_pareto.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="55">
   <si>
     <t>run_id</t>
   </si>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>2026_05_13_21_49</t>
+  </si>
+  <si>
+    <t>2026_05_14_21_18</t>
   </si>
 </sst>
 </file>
@@ -533,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -1469,6 +1472,50 @@
         <v>53</v>
       </c>
     </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22">
+        <v>5</v>
+      </c>
+      <c r="E22">
+        <v>9999</v>
+      </c>
+      <c r="F22">
+        <v>77</v>
+      </c>
+      <c r="G22">
+        <v>91</v>
+      </c>
+      <c r="H22">
+        <v>77.09099999999999</v>
+      </c>
+      <c r="I22">
+        <v>77.09099999999999</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>2.626000165939331</v>
+      </c>
+      <c r="L22">
+        <v>2</v>
+      </c>
+      <c r="M22">
+        <v>5</v>
+      </c>
+      <c r="N22" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
